--- a/data/trans_dic/IP07_C15_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Estudios-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 53,85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 51,45</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,56</t>
+          <t>0,0; 31,13</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 17,26</t>
+          <t>6,73; 14,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,52</t>
+          <t>8,07; 18,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 14,97</t>
+          <t>8,53; 15,05</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 22,43</t>
+          <t>4,02; 21,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 23,09</t>
+          <t>3,24; 22,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 19,0</t>
+          <t>5,18; 18,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,25</t>
+          <t>7,5; 15,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,06</t>
+          <t>8,34; 16,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,19</t>
+          <t>8,61; 13,98</t>
         </is>
       </c>
     </row>
@@ -774,18 +774,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2604</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 8363</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 7932</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8512</t>
+          <t>0; 8637</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>37278</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9328; 26230</t>
+          <t>12615; 27433</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13397; 29467</t>
+          <t>10906; 24450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26319; 51176</t>
+          <t>27505; 48537</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8527</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1092; 8101</t>
+          <t>1831; 9655</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1816; 10408</t>
+          <t>1235; 8728</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4661; 15427</t>
+          <t>4335; 15272</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11854; 30319</t>
+          <t>18627; 37449</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19212; 40210</t>
+          <t>15458; 30076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36702; 63756</t>
+          <t>37331; 60644</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C15_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 53,85</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,73; 14,64</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,07; 18,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,53; 15,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,02; 21,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,24; 22,9</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,18; 18,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,5; 15,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,34; 16,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 13,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1676624459309503</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.09386628141256949</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 8363</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 8637</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5384520228806656</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0.3113191418821729</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1027665924912533</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1334551355562647</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1156238416057798</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19252</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37278</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.0673400277456128</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.08074029233617278</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.08531152251147674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12615; 27433</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10906; 24450</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27505; 48537</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1464423032152508</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1810105088609873</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1505442543601569</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1012661284269016</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1027917550712286</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1019614156680825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3918</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8527</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.04023519931449748</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03239683867026671</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.05183084315450385</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1831; 9655</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1235; 8728</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4335; 15272</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2121123047754629</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2290072662541594</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1826158888143132</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1065495886581912</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1183621320570187</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1115983309592058</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>26465</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>21944</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48409</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.07499174689289642</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.08337657299074749</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.08605981245352706</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>18627; 37449</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15458; 30076</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>37331; 60644</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1507715250547991</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1622219595541471</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1398032517546698</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2604</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8363</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>8637</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>19252</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>18027</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>37278</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12615</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>10906</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>27505</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>27433</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>24450</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>48537</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4609</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3918</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>8527</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1235</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9655</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8728</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>15272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>26465</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>21944</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>48409</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>18627</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>15458</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>37331</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>37449</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>30076</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>60644</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>